--- a/Assets/MFramework_Test/Excel/TestTable.xlsx
+++ b/Assets/MFramework_Test/Excel/TestTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>参数1</t>
   </si>
@@ -23,10 +23,31 @@
     <t>参数3</t>
   </si>
   <si>
-    <t>No.1值</t>
+    <t>参数1(1)</t>
   </si>
   <si>
-    <t>No.2值</t>
+    <t>参数2(1)</t>
+  </si>
+  <si>
+    <t>参数3(1)</t>
+  </si>
+  <si>
+    <t>参数1(2)</t>
+  </si>
+  <si>
+    <t>参数2(2)</t>
+  </si>
+  <si>
+    <t>参数3(2)</t>
+  </si>
+  <si>
+    <t>参数1(3新增)</t>
+  </si>
+  <si>
+    <t>参数2(3新增)</t>
+  </si>
+  <si>
+    <t>参数3(3新增)</t>
   </si>
 </sst>
 </file>
@@ -72,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91,21 +112,32 @@
         <v>3</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
